--- a/consent_forms/025_voter_registration_records_release_form--consent_forms.xlsx
+++ b/consent_forms/025_voter_registration_records_release_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Voter Registration Records Release Form</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -576,7 +576,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A form to request access to voter registration records.</t>
+          <t>A form to request access to voter registration records</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -593,12 +593,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_requested_by</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Requested by</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -611,17 +611,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_requested_by</t>
+          <t>form_request_date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Requested by</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -634,17 +634,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_requested_by</t>
+          <t>form_request_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Requested by</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -662,12 +662,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_requested_by</t>
+          <t>form_reason</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Requested by</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,12 +685,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_requested_by</t>
+          <t>form_requested_by_title</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Requested by</t>
+          <t>Name or Title</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -708,12 +708,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_requested_by</t>
+          <t>form_requested_by_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Requested by</t>
+          <t>Form Requested By 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -726,17 +726,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_requested_by</t>
+          <t>form_request_date_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Requested by</t>
+          <t>Form Request Date 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -749,17 +749,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_requested_by</t>
+          <t>form_request_time_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Requested by</t>
+          <t>Form Request Time 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -777,108 +777,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_requested_by</t>
+          <t>form_reason_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Requested by</t>
+          <t>Form Reason 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_requested_by</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Requested by</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>form_requested_by</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Requested by</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_requested_by</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Requested by</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>form_requested_by</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Requested by</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
